--- a/data/trans_orig/IP1013-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP1013-Provincia-trans_orig.xlsx
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4015</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75779</t>
+          <t>75218</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>149957</t>
+          <t>150554</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2526</t>
+          <t>3377</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38676</t>
+          <t>38658</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>84169</t>
+          <t>83318</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3581</t>
+          <t>3536</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>154323</t>
+          <t>154368</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>318728</t>
+          <t>318776</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4428</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5737</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,37%</t>
         </is>
       </c>
     </row>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>676593</t>
+          <t>677199</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>719324</t>
+          <t>718659</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1397984</t>
+          <t>1398516</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>3292</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3410</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64496</t>
+          <t>64886</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>135352</t>
+          <t>134850</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>3363</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5232,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>78919</t>
+          <t>78871</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>156626</t>
+          <t>156573</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3527</t>
+          <t>3511</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>56718</t>
+          <t>56734</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>112779</t>
+          <t>112754</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3114</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4571</t>
+          <t>4862</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>134769</t>
+          <t>135098</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>142625</t>
+          <t>142408</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>279886</t>
+          <t>279595</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2831</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>161844</t>
+          <t>161405</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>333192</t>
+          <t>332190</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>656</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>624</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5655</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>8782</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>701128</t>
+          <t>701139</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>706269</t>
+          <t>706272</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>742487</t>
+          <t>742835</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>747517</t>
+          <t>747518</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1446765</t>
+          <t>1446288</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1453706</t>
+          <t>1453093</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5075</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>4548</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -8863,7 +8863,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>39128</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>85343</t>
+          <t>85240</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3523</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>3553</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>133851</t>
+          <t>133598</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>277456</t>
+          <t>277893</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>597</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5993</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,39 +10137,39 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5732</t>
+          <t>5655</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>699065</t>
+          <t>698378</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>704371</t>
+          <t>703774</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,39 +10250,39 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -10305,7 +10305,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1443483</t>
+          <t>1443560</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">

--- a/data/trans_orig/IP1013-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP1013-Provincia-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -840,42 +840,42 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>52568</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -953,52 +953,52 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>52568</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>52568</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>52568</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1178,47 +1178,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>101562</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1521,47 +1521,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>67597</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,107 +1751,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>673</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3366</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>673</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3893</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3367</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>4,92%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3418</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>78438</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>75745</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,15%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,75%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>74861</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>78438</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>75218</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>150554</t>
+          <t>150605</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,107 +2094,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>622</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3194</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3152</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,49%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,63%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>7,53%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3125</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3377</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>41230</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>38658</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>38700</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>41852</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,51%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92,37%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>92,47%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>124</t>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>83318</t>
+          <t>83570</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2550,47 +2550,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>56055</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2893,47 +2893,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>128622</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3123,72 +3123,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3536</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3598</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3186</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3236,74 +3236,74 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>157262</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>154368</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>154306</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>99,59%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>97,76%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>97,72%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>493</t>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>318776</t>
+          <t>318759</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3349,57 +3349,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3466,72 +3466,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>3375</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>1264</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>3822</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>4443</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>4041</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>625</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -3579,74 +3579,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>722027</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>719325</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,91%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>99,53%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>679757</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>677199</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>676578</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,81%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>99,44%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>99,35%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>722027</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>718659</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>99,44%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>2101</t>
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1398516</t>
+          <t>1398333</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1403100</t>
+          <t>1403096</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3692,57 +3692,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3877,7 +3877,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4158,47 +4158,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>52964</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4271,57 +4271,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4501,47 +4501,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>104713</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -4614,57 +4614,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4731,107 +4731,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>731</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3292</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3695</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,07%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,83%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>5,42%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3673</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>731</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3912</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -4844,74 +4844,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>67447</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>64886</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>64483</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>68178</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,93%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>95,17%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>94,58%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>194</t>
@@ -4924,7 +4924,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>134850</t>
+          <t>135089</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4957,57 +4957,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5074,107 +5074,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>668</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>668</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3363</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3543</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3422</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -5187,72 +5187,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>81566</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>78810</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,84%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>81566</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>78871</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>156573</t>
+          <t>156452</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5300,57 +5300,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5530,47 +5530,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>43901</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -5643,57 +5643,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5760,107 +5760,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>687</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3547</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>687</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3511</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3439</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>5,83%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>3476</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -5873,72 +5873,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>59558</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>56698</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>98,86%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>94,11%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>59558</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>56734</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>98,86%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>112754</t>
+          <t>112791</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5986,57 +5986,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6108,102 +6108,102 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3564</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
           <t>685</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>3620</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3824</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,49%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>3331</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1308</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>4284</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1308</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>4862</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -6216,74 +6216,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>145115</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>142175</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>97,55%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>138033</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>135098</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>134894</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>138718</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,51%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>97,39%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>97,24%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>145115</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>142408</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,57%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>97,71%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>398</t>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>279595</t>
+          <t>280173</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6329,57 +6329,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6446,107 +6446,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3303</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3802</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>3326</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>661</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>3833</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -6559,74 +6559,74 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>164047</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>161405</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>160906</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>164708</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>99,6%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>97,99%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>97,69%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>497</t>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>332190</t>
+          <t>332697</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6672,57 +6672,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6794,67 +6794,67 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>1979</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>5301</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
           <t>2076</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>5789</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5725</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>1979</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>5307</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8782</t>
+          <t>8572</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -6902,74 +6902,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>746163</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>742841</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>747519</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,74%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>99,29%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>704852</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>701139</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>706272</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>701203</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>706268</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,71%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>99,18%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>99,91%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1063</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>746163</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>742835</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>747518</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,74%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>99,29%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,92%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>2078</t>
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1446288</t>
+          <t>1446498</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1453093</t>
+          <t>1453716</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,91%</t>
         </is>
       </c>
     </row>
@@ -7015,57 +7015,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7189,7 +7189,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -7200,7 +7200,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -7481,47 +7481,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>57371</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -7594,57 +7594,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7824,47 +7824,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>103947</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -7937,57 +7937,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8167,47 +8167,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>66831</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -8280,57 +8280,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8510,47 +8510,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>76961</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -8623,57 +8623,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8740,107 +8740,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1368</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4310</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4604</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>3,15%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,92%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>10,6%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1368</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>5384</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1368</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4548</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -8853,74 +8853,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>42070</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>39128</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>38834</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>43438</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>96,85%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>90,08%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>89,4%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>129</t>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>85240</t>
+          <t>84404</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -8966,57 +8966,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9196,47 +9196,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>54273</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -9309,57 +9309,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9426,107 +9426,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>705</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>3776</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3513</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,51%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>3156</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>3553</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -9539,74 +9539,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>136669</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>133598</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>133861</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>137374</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,49%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>97,25%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>97,44%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>414</t>
@@ -9619,7 +9619,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>277893</t>
+          <t>278290</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9652,57 +9652,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9882,47 +9882,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>164176</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -9995,57 +9995,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10112,72 +10112,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>2074</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>5993</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>6099</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,08%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>596</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5655</t>
+          <t>5875</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -10225,74 +10225,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1058</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>702297</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>698378</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>698272</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>703774</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,71%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>99,13%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>99,92%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>2123</t>
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1443560</t>
+          <t>1443340</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1448618</t>
+          <t>1448619</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10338,57 +10338,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
